--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="263">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -382,10 +382,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -894,10 +890,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>外鍵</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>productImages資料表(t_productImages)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1070,10 +1062,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>1代表其他分類; 詳情請見其他表</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>f_createTime</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -1084,6 +1072,22 @@
   <si>
     <t>f_createTime</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>uuid</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniqueidentifier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniqueidentifier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniqueidentifier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1279,6 +1283,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1287,12 +1297,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1618,14 +1622,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1770,14 +1774,14 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1832,7 +1836,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1898,14 +1902,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1966,7 +1970,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>28</v>
@@ -1983,17 +1987,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2003,48 +2007,48 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I8" t="s">
         <v>202</v>
-      </c>
-      <c r="I8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>35</v>
@@ -2054,13 +2058,13 @@
         <v>36</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>27</v>
@@ -2078,10 +2082,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2090,16 +2094,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2108,21 +2112,21 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2149,7 +2153,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2186,7 +2190,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>22</v>
@@ -2196,16 +2200,16 @@
         <v>29</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>22</v>
@@ -2215,35 +2219,35 @@
         <v>30</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -2287,14 +2291,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2307,10 +2311,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -2321,51 +2325,51 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2377,87 +2381,87 @@
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
@@ -2465,81 +2469,81 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
+      <c r="A14" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
@@ -2555,14 +2559,14 @@
       <c r="F19" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
+      <c r="A21" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="15"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2589,7 +2593,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
@@ -2601,13 +2605,13 @@
         <v>8</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
@@ -2623,33 +2627,33 @@
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2676,14 +2680,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2710,19 +2714,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -2731,38 +2733,36 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>258</v>
-      </c>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2771,36 +2771,36 @@
         <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2827,40 +2827,40 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="G10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2872,16 +2872,16 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
+      <c r="A14" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
       <c r="G14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2889,7 +2889,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -2909,19 +2909,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -2933,17 +2933,17 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -2955,63 +2955,63 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
+        <v>246</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
       <c r="M18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N18" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M19" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M20">
         <v>230</v>
@@ -3023,17 +3023,17 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -3048,73 +3048,73 @@
         <v>19</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="M23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>253</v>
-      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
+      <c r="A26" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -3134,19 +3134,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -3158,17 +3158,17 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>86</v>
+        <v>262</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -3180,25 +3180,25 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="15"/>
+        <v>247</v>
+      </c>
+      <c r="G30" s="11"/>
+      <c r="H30" s="12"/>
       <c r="M30" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3233,33 +3233,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3267,70 +3267,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" t="s">
         <v>178</v>
-      </c>
-      <c r="H7" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3341,7 +3341,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="H8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="262">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -952,10 +952,6 @@
   <si>
     <t>nvarchar(1500)</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>最多10項</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>nvarchar(30)</t>
@@ -2717,14 +2713,14 @@
         <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -2752,7 +2748,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
@@ -2762,7 +2758,7 @@
         <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2781,7 +2777,7 @@
         <v>224</v>
       </c>
       <c r="M7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2800,7 +2796,7 @@
         <v>225</v>
       </c>
       <c r="M8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2827,19 +2823,19 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="G10" t="s">
         <v>221</v>
@@ -2848,19 +2844,19 @@
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2873,16 +2869,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="15"/>
-      <c r="G14" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -2936,7 +2929,7 @@
         <v>96</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>86</v>
@@ -2958,22 +2951,22 @@
         <v>210</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>165</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
       <c r="M18" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" t="s">
         <v>254</v>
-      </c>
-      <c r="N18" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -2982,20 +2975,20 @@
         <v>219</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -3048,10 +3041,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -3063,40 +3056,40 @@
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="M23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -3161,7 +3154,7 @@
         <v>215</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>165</v>
@@ -3183,22 +3176,22 @@
         <v>210</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>165</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
       <c r="M30" t="s">
+        <v>236</v>
+      </c>
+      <c r="N30" t="s">
         <v>237</v>
-      </c>
-      <c r="N30" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="268">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -110,10 +110,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>默認為當前時間, 之後可以再改</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>f_status</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -454,10 +450,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>order流水號</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>外鍵</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -482,10 +474,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>datetime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -506,10 +494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>item流水號</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -535,10 +519,6 @@
   </si>
   <si>
     <t>f_orderId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">f_productId </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -562,10 +542,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -578,66 +554,34 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>varchar(20)</t>
+    <t>收件人電話號碼(允許國外)</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_address</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>若設為預設地址, 則儲存到會員地址</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中市</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>北屯區</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>遼寧路一段376號</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>N</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>收件人電話號碼(允許國外)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_address</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>varchar(20)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>若設為預設地址, 則儲存到會員地址</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>台中市</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>北屯區</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>遼寧路一段376號</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderRefund資料表(t_orderRefund)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderRefundId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(100)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>管理者描述退款原因</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_refundReason</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>數字越高, 等級越高, 方便擴充</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -650,10 +594,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>退款金額</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -798,10 +738,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>nvarchar(50)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>信箱</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1084,6 +1020,94 @@
   <si>
     <t>uniqueidentifier</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流水號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>流水號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(50)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(50)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(20)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(346)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>默認為當前時間, 之後更新</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>退款原因</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退款說明</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(25)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(150)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_returnDate</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_description</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_reason</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退款日期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>returnItems資料表(t_returnItems)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderReturns資料表(t_orderReturns)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderReturnId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_returnItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_styleId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_price</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>產品金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1619,7 +1643,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1632,13 +1656,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -1649,129 +1673,129 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1784,16 +1808,16 @@
         <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1804,68 +1828,68 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1923,7 @@
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1932,7 +1956,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -1950,7 +1974,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -1966,10 +1990,10 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>12</v>
@@ -1983,17 +2007,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2003,67 +2027,67 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="I8" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -2078,10 +2102,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2090,16 +2114,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2108,15 +2132,15 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -2149,7 +2173,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2161,13 +2185,13 @@
         <v>8</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>15</v>
@@ -2177,80 +2201,80 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24">
         <v>406</v>
@@ -2278,7 +2302,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A2:F26"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -2286,66 +2310,82 @@
     <col min="6" max="6" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="15"/>
+    </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="E2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
+      <c r="D3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
@@ -2353,120 +2393,116 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3" t="s">
-        <v>122</v>
+      <c r="A6" s="6"/>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>103</v>
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>249</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>232</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>232</v>
+      </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
-      <c r="B12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -2476,87 +2512,95 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>117</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2589,7 +2633,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
@@ -2601,13 +2645,13 @@
         <v>8</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
@@ -2617,46 +2661,171 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
-        <v>149</v>
+        <v>259</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>148</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="4" t="s">
-        <v>151</v>
+      <c r="A26" s="5"/>
+      <c r="B26" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>153</v>
+        <v>256</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>154</v>
-      </c>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="15"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2677,7 +2846,7 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -2696,13 +2865,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2710,17 +2879,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -2729,13 +2898,13 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -2745,67 +2914,67 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="M7" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="M8" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -2814,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2823,40 +2992,40 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="G10" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2869,7 +3038,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -2879,10 +3048,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -2902,19 +3071,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -2926,17 +3095,17 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -2948,63 +3117,63 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
       <c r="M18" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="N18" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M20">
         <v>230</v>
@@ -3016,17 +3185,17 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -3038,63 +3207,63 @@
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -3104,10 +3273,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -3127,19 +3296,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -3151,17 +3320,17 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -3173,25 +3342,25 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
       <c r="M30" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="N30" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3227,7 +3396,7 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -3237,22 +3406,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3260,70 +3429,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="H7" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3334,7 +3503,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="296">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -166,10 +166,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>f_memberId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>f_memberAccount</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -182,10 +178,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>memberAddress資料表(t_memberAddress)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -294,10 +286,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_uid</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -358,10 +346,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_roleId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>描述腳色的用途</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -406,10 +390,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">f_updated_at </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>數據行名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -454,7 +434,191 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>decimal</t>
+    <t>訂單狀態</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>默認為當前時間</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據行名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>說明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>identity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_totalPrice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>分成 "1:普通會員, 2:白銀會員, 3:鑽石會員"</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>街道, 巷弄, 門號, 樓層</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>給予較大寬容度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_recipientName</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderItems資料表(t_orderItems)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人姓名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_phone</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人電話號碼(允許國外)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_address</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>若設為預設地址, 則儲存到會員地址</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中市</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>北屯區</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>遼寧路一段376號</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>數字越高, 等級越高, 方便擴充</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_refundAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退款金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>transactions資料表(t_transactions)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據行名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料類型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>預設值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>說明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_transactionId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>identity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction流水號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_amount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -462,278 +626,66 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>訂單狀態</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">f_created_at </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>默認為當前時間</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>KEY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據行名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>說明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>identity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t xml:space="preserve">f_transactionType </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex : 付款, 退款</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>當訂單狀態 status 為4:買家取件成功, 則新增1筆交易紀錄</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>當訂單狀態status 為 12:退款完成, 則新增1筆交易紀錄</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(300)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(6)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>members資料表(t_members)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_status</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(25)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_points</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>外鍵參照</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_memberId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_totalPrice</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_itemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>分成 "1:普通會員, 2:白銀會員, 3:鑽石會員"</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>街道, 巷弄, 門號, 樓層</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>給予較大寬容度</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_recipientName</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderItems資料表(t_orderItems)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人姓名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_phone</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人電話號碼(允許國外)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_address</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>若設為預設地址, 則儲存到會員地址</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>台中市</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>北屯區</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>遼寧路一段376號</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>數字越高, 等級越高, 方便擴充</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_refundAmount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>退款金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>transactions資料表(t_transactions)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KEY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據行名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資料類型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>預設值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>說明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_transactionId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>identity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction流水號</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>外鍵</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_amount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>金額</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">f_transactionType </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex : 付款, 退款</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>當訂單狀態 status 為4:買家取件成功, 則新增1筆交易紀錄</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>當訂單狀態status 為 12:退款完成, 則新增1筆交易紀錄</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(300)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>char(6)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>members資料表(t_members)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_status</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(25)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_points</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>tinyint</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -748,10 +700,6 @@
   <si>
     <t>積分（代表年度消費金額）</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_addressId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>f_district</t>
@@ -830,15 +778,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_productImageId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>f_productId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productStyleId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -998,10 +938,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>f_lastShelveEditTime</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>f_createTime</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -1046,18 +982,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>默認為當前時間, 之後更新</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>退款原因</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>退款說明</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>nvarchar(25)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1078,10 +1002,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>退款日期</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>returnItems資料表(t_returnItems)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1108,6 +1028,196 @@
   <si>
     <t>產品金額</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_lastEditTime</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>分類代號(名稱寫在前端)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>外鍵</t>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退貨原因</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退貨說明</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退貨日期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinyint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退款狀態 (未退款/已退款</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_returnStatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_refundStatus</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>加上訂單的送貨資訊?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">黑貓, </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>qwpe486wqel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ex: seven ,</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註:幾點要出貨, 或者說是取消訂單的原因等等</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(50)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>流水號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>外鍵參照</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>外鍵要說明是甚麼外鍵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>外鍵參照</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productStyleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有命名符合規律</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_createTime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>status 寫出所有狀態</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>總金額 (decimal 要設定 小數點前 小數點後幾位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_information</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註的英文</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>數量設計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以設計另一張訂單紀錄表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退貨單狀態 (已確認/取消</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>設計需要 包含需要的資訊(EX時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_ordersId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_membersId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderItemsId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderReturnsId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_returnItemsId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_producstId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productStylesId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productImagesId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>memberAddresses資料表(t_memberAddresses)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_addressesId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_usersId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_rolesId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1269,7 +1379,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1317,6 +1427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1643,7 +1756,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1656,13 +1769,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -1673,73 +1786,73 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>294</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1748,54 +1861,54 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1808,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1828,68 +1941,68 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1923,7 +2036,7 @@
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1956,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -1974,7 +2087,7 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -1990,7 +2103,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
@@ -2007,17 +2120,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2027,64 +2140,64 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>26</v>
@@ -2102,10 +2215,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2114,16 +2227,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2132,15 +2245,15 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -2173,7 +2286,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>178</v>
+        <v>293</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2210,7 +2323,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
@@ -2220,16 +2333,16 @@
         <v>28</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>21</v>
@@ -2239,35 +2352,35 @@
         <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -2302,25 +2415,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" customWidth="1"/>
     <col min="6" max="6" width="47.6640625" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
       <c r="F1" s="15"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="J1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2331,68 +2452,71 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>116</v>
+        <v>284</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
-        <v>117</v>
+        <v>285</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -2401,206 +2525,236 @@
         <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>232</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H13" t="s">
+        <v>263</v>
+      </c>
+      <c r="J13">
+        <v>23145677</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="15"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>261</v>
+      </c>
+      <c r="J14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>279</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -2608,7 +2762,7 @@
       <c r="E21" s="14"/>
       <c r="F21" s="15"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -2628,12 +2782,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>7</v>
@@ -2645,13 +2799,13 @@
         <v>8</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
@@ -2664,168 +2818,297 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
-        <v>137</v>
+        <v>259</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>138</v>
+        <v>255</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>126</v>
+        <v>256</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="15"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B34" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F34" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="6"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+      <c r="B42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="4" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
+      <c r="C44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3" t="s">
+        <v>247</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2846,7 +3129,7 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -2865,13 +3148,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2879,17 +3162,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -2898,74 +3181,76 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M6" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="M7" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="M8" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2974,7 +3259,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -2983,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2992,40 +3277,40 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="G10" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -3038,7 +3323,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -3048,10 +3333,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -3071,19 +3356,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -3095,17 +3380,17 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -3117,63 +3402,63 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
       <c r="M18" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="N18" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M20">
         <v>230</v>
@@ -3185,17 +3470,17 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -3210,60 +3495,60 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -3273,10 +3558,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -3296,19 +3581,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>198</v>
+        <v>291</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -3320,17 +3605,17 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -3342,25 +3627,25 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
       <c r="M30" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="N30" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3396,7 +3681,7 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -3406,22 +3691,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3429,70 +3714,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3503,7 +3788,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="H8" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="299">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -270,10 +270,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>users資料表(t_users)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>數據行名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -334,10 +330,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>roles資料表(t_roles)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NULL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -350,10 +342,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>products資料表(t_products)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NULL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -410,10 +398,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>orders資料表(t_orders)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NULL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -490,10 +474,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>orderItems資料表(t_orderItems)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -664,10 +644,6 @@
   <si>
     <t>char(6)</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>members資料表(t_members)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>f_status</t>
@@ -774,10 +750,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>productImages資料表(t_productImages)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>f_productId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -834,10 +806,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>productStyles資料表(t_productStyles)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>nvarchar(25)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -1002,14 +970,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>returnItems資料表(t_returnItems)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderReturns資料表(t_orderReturns)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>f_orderReturnId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1172,51 +1132,103 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>f_ordersId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_membersId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderItemsId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderReturnsId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_returnItemsId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_producstId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productStylesId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productImagesId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>memberAddresses資料表(t_memberAddresses)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_addressesId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_usersId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_rolesId</t>
+    <t>productImage資料表(t_productImage)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productImageId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據行名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productStyleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>productStyle資料表(t_productStyle)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_producsId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>product資料表(t_product)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderItem資料表(t_orderItem)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderReturn資料表(t_orderReturn)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>order資料表(t_order)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_memberId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderReturnId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>returnItem資料表(t_returnItem)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_returnItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>returnItem資料表(t_returnItem)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>member資料表(t_member)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_memberId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>memberAddress資料表(t_memberAddress)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_addressId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user資料表(t_user)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_userId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_roleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>role資料表(t_role)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1419,6 +1431,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1427,9 +1442,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1755,27 +1767,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="A2" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -1786,28 +1798,28 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>50</v>
@@ -1823,20 +1835,20 @@
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1845,7 +1857,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>37</v>
@@ -1861,7 +1873,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>35</v>
@@ -1876,17 +1888,17 @@
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -1907,14 +1919,14 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15"/>
+      <c r="A13" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1927,10 +1939,10 @@
         <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1941,7 +1953,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>56</v>
@@ -1969,7 +1981,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1981,11 +1993,11 @@
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2035,14 +2047,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="A2" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2069,7 +2081,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -2103,7 +2115,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
@@ -2120,17 +2132,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2140,48 +2152,48 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>33</v>
@@ -2191,13 +2203,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>26</v>
@@ -2215,10 +2227,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2227,16 +2239,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2245,21 +2257,21 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
+      <c r="A17" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2286,7 +2298,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2323,7 +2335,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
@@ -2333,16 +2345,16 @@
         <v>28</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>21</v>
@@ -2352,35 +2364,35 @@
         <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -2426,19 +2438,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16" t="s">
-        <v>273</v>
+      <c r="A1" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="13" t="s">
+        <v>263</v>
       </c>
       <c r="J1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2452,10 +2464,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -2466,22 +2478,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>283</v>
+        <v>223</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2490,30 +2502,30 @@
         <v>285</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2525,102 +2537,102 @@
         <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2631,136 +2643,136 @@
       <c r="E12" s="2"/>
       <c r="F12" s="3"/>
       <c r="H12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H13" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="J13">
         <v>23145677</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
+      <c r="A14" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
       <c r="H14" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="J14" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>286</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
+      <c r="A21" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2799,13 +2811,13 @@
         <v>8</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
@@ -2821,39 +2833,39 @@
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="4" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -2863,66 +2875,66 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
+      <c r="A32" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -2949,7 +2961,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>7</v>
@@ -2961,13 +2973,13 @@
         <v>8</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -2977,13 +2989,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>7</v>
@@ -2993,7 +3005,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -3005,14 +3017,14 @@
       <c r="F37" s="3"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
+      <c r="A39" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -3039,7 +3051,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>7</v>
@@ -3051,13 +3063,13 @@
         <v>8</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -3067,13 +3079,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -3089,17 +3101,17 @@
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="4" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3128,14 +3140,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="A2" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3148,13 +3160,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3162,17 +3174,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -3181,38 +3193,38 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -3221,36 +3233,36 @@
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M7" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="M8" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -3268,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -3277,40 +3289,40 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -3322,21 +3334,21 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
+      <c r="A14" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>88</v>
+        <v>276</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -3356,19 +3368,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -3380,17 +3392,17 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -3402,63 +3414,63 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
       <c r="M18" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M20">
         <v>230</v>
@@ -3470,17 +3482,17 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -3495,73 +3507,73 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="M23" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
+      <c r="A26" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -3581,19 +3593,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -3605,17 +3617,17 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -3627,25 +3639,25 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
       <c r="M30" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N30" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3680,33 +3692,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="A2" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3714,70 +3726,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H7" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3788,7 +3800,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="H8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="訂單表" sheetId="9" r:id="rId3"/>
     <sheet name="商品表" sheetId="5" r:id="rId4"/>
     <sheet name="交易紀錄表" sheetId="10" r:id="rId5"/>
+    <sheet name="備用(淘汰的表)" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="313">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -226,10 +227,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>一串數字, 用來表示擁有的權限, 採用的方式是根據C# enum的設計</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>identity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -338,10 +335,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>描述腳色的用途</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>NULL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -366,14 +359,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>decimal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>價格</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -414,251 +399,231 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>訂單狀態</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據行名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>說明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>identity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_totalPrice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>街道, 巷弄, 門號, 樓層</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>給予較大寬容度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_recipientName</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人姓名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_phone</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_address</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>若設為預設地址, 則儲存到會員地址</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中市</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>北屯區</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>遼寧路一段376號</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_refundAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退款金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>transactions資料表(t_transactions)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據行名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料類型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>預設值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>說明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_transactionId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>identity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction流水號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>外鍵</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>訂單狀態</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>默認為當前時間</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>KEY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據行名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>說明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>identity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>f_amount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>f_totalPrice</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderId</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>分成 "1:普通會員, 2:白銀會員, 3:鑽石會員"</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>街道, 巷弄, 門號, 樓層</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>給予較大寬容度</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_recipientName</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>金額</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">f_transactionType </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人姓名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_phone</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人電話號碼(允許國外)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_address</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>若設為預設地址, 則儲存到會員地址</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>台中市</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>北屯區</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>遼寧路一段376號</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ex : 付款, 退款</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>當訂單狀態 status 為4:買家取件成功, 則新增1筆交易紀錄</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>當訂單狀態status 為 12:退款完成, 則新增1筆交易紀錄</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>數字越高, 等級越高, 方便擴充</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_refundAmount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(300)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(6)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_status</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(25)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_points</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>退款金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>transactions資料表(t_transactions)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KEY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據行名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資料類型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>預設值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>說明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_transactionId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>identity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction流水號</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>外鍵</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_amount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>金額</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">f_transactionType </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex : 付款, 退款</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>當訂單狀態 status 為4:買家取件成功, 則新增1筆交易紀錄</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>當訂單狀態status 為 12:退款完成, 則新增1筆交易紀錄</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(300)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>char(6)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_status</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(25)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_points</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -674,10 +639,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>積分（代表年度消費金額）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>f_district</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -707,10 +668,6 @@
   </si>
   <si>
     <t>大部分會員都是台灣, 所以使用char 即使變動 長度也不變</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色名字 unique</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -930,10 +887,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>流水號</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>nvarchar(50)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -998,13 +951,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>外鍵</t>
-  </si>
-  <si>
-    <t>?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>退貨原因</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1037,29 +983,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>加上訂單的送貨資訊?</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">黑貓, </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>qwpe486wqel</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ex: seven ,</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>備註:幾點要出貨, 或者說是取消訂單的原因等等</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>nvarchar(50)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1068,26 +991,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>外鍵參照</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>外鍵要說明是甚麼外鍵</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>外鍵參照</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>f_productStyleId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_orderItemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>所有命名符合規律</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1100,26 +1007,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>總金額 (decimal 要設定 小數點前 小數點後幾位)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_information</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>備註的英文</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>decimal</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>數量設計</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>可以設計另一張訂單紀錄表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1128,10 +1019,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>設計需要 包含需要的資訊(EX時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>productImage資料表(t_productImage)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1160,76 +1047,253 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>orderItem資料表(t_orderItem)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>order資料表(t_order)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_memberId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderReturnId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>member資料表(t_member)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_memberId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>memberAddress資料表(t_memberAddress)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_addressId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user資料表(t_user)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_userId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_roleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>role資料表(t_role)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>退貨單外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單商品項目外鍵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_quantity</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>數量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>orderReturn資料表(t_orderReturn)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>datetime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderStateId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_state</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinyint</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderState資料表(t_orderState)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_updateTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>datetime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_remark</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_remark</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要嗎?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>f_orderId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>order資料表(t_order)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_memberId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderItemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderReturnId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>流水號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單編號設計需要 包含需要的資訊(EX時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>returnItem資料表(t_returnItem)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_returnItemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>returnItem資料表(t_returnItem)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>member資料表(t_member)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_memberId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>memberAddress資料表(t_memberAddress)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_addressId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>user資料表(t_user)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_userId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_roleId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>role資料表(t_role)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderProductStyle資料表(t_orderProductStyle)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderProductStyleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>會員表外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單表外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人電話號碼 (允許國外)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品子項目 (細項) 表外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單表外鍵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註 (舉例:幾點要出貨, 或者說是取消訂單的原因...等等)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>依照階級往上數分成 "1:普通會員, 2:白銀會員,
+ 3:鑽石會員"</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>積分 (代表年度消費金額)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>一串數字, 用來表示擁有的權限, 
+採用的方式是根據C# enum的設計</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色名字</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述腳色的用途</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單更新就會生成對應state, ( 1:待確認訂單, 
+2:待出貨, 3:已出貨, 4:取件成功, 5:買家未取商品, 
+6:重新寄回, 7:取消, 8:退貨)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註 (Ex:取消原因, 退貨瑕疵?)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>總金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>產品金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>價格 (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderNumber</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期時間 (YYYYMMDD) + 分隔號 (-) + 序列號 (5碼), 序列號表當日第N筆訂單
+  (Ex:20250106-00001 、 20250107-00002)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(14)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示生成這個狀態的時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1391,7 +1455,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1433,6 +1497,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1758,7 +1825,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表4"/>
-  <dimension ref="A2:G18"/>
+  <dimension ref="A2:G19"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -1767,27 +1834,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -1798,57 +1865,57 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1857,14 +1924,14 @@
         <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1873,7 +1940,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>35</v>
@@ -1882,30 +1949,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>36</v>
@@ -1918,15 +1985,23 @@
         <v>38</v>
       </c>
     </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+    </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
+      <c r="A13" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1936,13 +2011,13 @@
         <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1953,16 +2028,16 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>41</v>
@@ -1981,7 +2056,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>168</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1993,18 +2068,18 @@
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>46</v>
@@ -2013,9 +2088,17 @@
         <v>35</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="F18" s="14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2047,14 +2130,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2081,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -2115,7 +2198,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
@@ -2132,17 +2215,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2152,48 +2235,48 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="I8" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>33</v>
@@ -2203,13 +2286,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>26</v>
@@ -2227,10 +2310,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2239,16 +2322,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2256,22 +2339,27 @@
       <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>119</v>
-      </c>
+      <c r="F13" s="14" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="A17" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2298,7 +2386,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2335,7 +2423,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
@@ -2345,16 +2433,16 @@
         <v>28</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>21</v>
@@ -2364,35 +2452,35 @@
         <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -2427,7 +2515,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -2435,22 +2523,23 @@
     <col min="6" max="6" width="47.6640625" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
     <col min="10" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
       <c r="G1" s="13" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="J1" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2464,10 +2553,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -2478,649 +2567,430 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="G3" s="13" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>103</v>
+        <v>309</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="3" t="s">
-        <v>266</v>
+      <c r="F5" s="14" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
-        <v>18</v>
+      <c r="A6" s="5"/>
+      <c r="B6" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>303</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>304</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>114</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>267</v>
+        <v>105</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>241</v>
+        <v>289</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="14" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="F12" s="3"/>
-      <c r="H12" t="s">
-        <v>250</v>
-      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J13">
-        <v>23145677</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="H14" t="s">
-        <v>251</v>
-      </c>
-      <c r="J14" t="s">
-        <v>252</v>
-      </c>
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="A15" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>261</v>
+        <v>98</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="4" t="s">
-        <v>236</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>109</v>
+        <v>15</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="17"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="B26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="4" t="s">
-        <v>248</v>
+      <c r="F26" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="3" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>246</v>
+        <v>273</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>86</v>
+        <v>278</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="F29" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="4" t="s">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>121</v>
+        <v>236</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="5"/>
-      <c r="B42" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A39:F39"/>
+  <mergeCells count="3">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3140,14 +3010,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3160,13 +3030,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3174,17 +3044,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -3193,38 +3063,38 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -3233,36 +3103,36 @@
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="M7" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="M8" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -3271,7 +3141,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -3280,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -3289,40 +3159,40 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -3334,21 +3204,21 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="A14" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -3368,19 +3238,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -3392,17 +3262,17 @@
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -3414,63 +3284,63 @@
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
       <c r="M18" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="N19" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="M20">
         <v>230</v>
@@ -3482,17 +3352,17 @@
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -3507,73 +3377,73 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="M23" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="A26" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>2</v>
@@ -3593,19 +3463,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -3617,17 +3487,17 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -3639,25 +3509,25 @@
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
       <c r="M30" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="N30" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3692,33 +3562,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3726,70 +3596,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="H7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3800,7 +3670,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -3819,4 +3689,320 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:G21"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="47.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="6"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:F14"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="317">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1184,10 +1184,6 @@
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderProductStyle資料表(t_orderProductStyle)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1283,16 +1279,36 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期時間 (YYYYMMDD) + 分隔號 (-) + 序列號 (5碼), 序列號表當日第N筆訂單
-  (Ex:20250106-00001 、 20250107-00002)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>char(14)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>表示生成這個狀態的時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderProductStyle資料表(t_orderProductStyle)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(15)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期時間 (YYYYMMDD) + 分類(2碼)+ 序列號 (5碼), 序列號表當日第N筆訂單 , UNIQUE有唯一性
+  (Ex:202501060300001 、 202501070500002)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_updateTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>創建時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(備註)更新時間</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2056,7 +2072,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2072,7 +2088,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2089,7 +2105,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2322,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
@@ -2340,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -2598,13 +2614,13 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>311</v>
@@ -2614,7 +2630,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="14" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2623,14 +2639,14 @@
         <v>97</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>243</v>
@@ -2681,7 +2697,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2709,11 +2725,11 @@
         <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2730,19 +2746,34 @@
       <c r="E12" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3"/>
+      <c r="B13" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G13" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -2775,7 +2806,7 @@
         <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>88</v>
@@ -2803,7 +2834,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2819,7 +2850,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2844,14 +2875,14 @@
         <v>224</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2925,7 +2956,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -2941,7 +2972,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2959,7 +2990,7 @@
         <v>198</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2975,7 +3006,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -3333,14 +3364,14 @@
         <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M20">
         <v>230</v>

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="304">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -399,10 +399,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>訂單狀態</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -635,10 +631,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>電話</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>f_district</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -655,15 +647,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>char(20)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>varchar(254)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>字數計算(+886) 0928969334</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -727,10 +711,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>預警可以設定在config檔案</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>nvarchar(40)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -771,38 +751,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>肉泥</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>~</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>~</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>eqlewp/eqw/123</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>/4448</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>雞肉</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>鮪魚1箱</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以新增描述規範</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -851,14 +799,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>EEWE</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>/WEQ42</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>f_createTime</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -895,14 +835,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>char(20)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(346)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>nvarchar(25)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -983,10 +915,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>nvarchar(50)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>流水號</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -995,26 +923,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>所有命名符合規律</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>f_createTime</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>status 寫出所有狀態</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>decimal</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>可以設計另一張訂單紀錄表</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>退貨單狀態 (已確認/取消</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1119,39 +1035,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>f_orderStateId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_state</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tinyint</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderState資料表(t_orderState)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_updateTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>datetime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderStateId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_state</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>tinyint</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderState資料表(t_orderState)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_updateTime</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>datetime</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1159,10 +1067,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>f_remark</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>需要嗎?</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1175,10 +1079,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>訂單編號設計需要 包含需要的資訊(EX時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>returnItem資料表(t_returnItem)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1191,20 +1091,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>會員表外鍵</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>訂單表外鍵</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人電話號碼 (允許國外)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>商品子項目 (細項) 表外鍵</t>
@@ -1241,74 +1133,130 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>訂單更新就會生成對應state, ( 1:待確認訂單, 
-2:待出貨, 3:已出貨, 4:取件成功, 5:買家未取商品, 
+    <t>備註 (Ex:取消原因, 退貨瑕疵?)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>總金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>產品金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10,2)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>價格 (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderNumber</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示生成這個狀態的時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderProductStyle資料表(t_orderProductStyle)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(15)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>創建時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(備註)更新時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingMethod</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前提供 1便利商店; 2:宅配</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單更新就會生成對應state, ( 1:待確認, 
+2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 
 6:重新寄回, 7:取消, 8:退貨)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>備註 (Ex:取消原因, 退貨瑕疵?)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>decimal(10,2)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>總金額  (小數點前8位 小數點後2位)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>decimal(10,2)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>產品金額  (小數點前8位 小數點後2位)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>decimal(10,2)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>價格 (小數點前8位 小數點後2位)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderNumber</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>表示生成這個狀態的時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderProductStyle資料表(t_orderProductStyle)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>char(15)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>update</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期時間 (YYYYMMDD) + 分類(2碼)+ 序列號 (5碼), 序列號表當日第N筆訂單 , UNIQUE有唯一性
+    <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_state</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示修改備註的時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_createTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>不管配送方式, 地址都須手動填寫</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>王六仔</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(326)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期時間 (YYMMDD) + 時分秒轉成秒(00000~86399) + 分類(2碼)+ 會員碼最末7位(EX:0000001)  UNIQUE有唯一性
   (Ex:202501060300001 、 202501070500002)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>f_updateTime</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>創建時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>(備註)更新時間</t>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人電話號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話號碼 (國內)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1471,7 +1419,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1525,6 +1473,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1851,7 +1808,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -1884,7 +1841,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -2011,7 +1968,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -2044,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>55</v>
@@ -2072,7 +2029,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2088,7 +2045,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2105,7 +2062,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="14" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2147,7 +2104,7 @@
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -2180,7 +2137,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -2214,7 +2171,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
@@ -2231,17 +2188,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2251,48 +2208,46 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>154</v>
+        <v>301</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>156</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="G8" s="8"/>
       <c r="I8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>33</v>
@@ -2302,13 +2257,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>26</v>
@@ -2326,10 +2281,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2338,16 +2293,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2356,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -2369,7 +2324,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -2402,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2439,7 +2394,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
@@ -2449,16 +2404,16 @@
         <v>28</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>21</v>
@@ -2468,35 +2423,35 @@
         <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -2531,7 +2486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -2542,23 +2497,18 @@
     <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
       <c r="F1" s="17"/>
-      <c r="G1" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="J1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2578,12 +2528,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>88</v>
@@ -2595,16 +2545,14 @@
         <v>47</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>88</v>
@@ -2614,48 +2562,49 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="48.6" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="14" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+      <c r="G5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>291</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2664,364 +2613,436 @@
         <v>89</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F7" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>302</v>
+      </c>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>215</v>
+        <v>299</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="32.4" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="14" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="14" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>270</v>
+        <v>184</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G13" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="1" t="s">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B19" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F19" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4" t="s">
-        <v>224</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>102</v>
+        <v>15</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="17"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="6"/>
+      <c r="B22" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="6"/>
+      <c r="B23" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="17"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="B28" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="F28" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3" t="s">
+      <c r="E29" s="2"/>
+      <c r="F29" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="14" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3032,7 +3053,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表3"/>
-  <dimension ref="A2:N31"/>
+  <dimension ref="A2:H31"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -3040,9 +3061,9 @@
     <col min="6" max="6" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -3050,7 +3071,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="17"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -3070,28 +3091,25 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
         <v>85</v>
@@ -3100,22 +3118,22 @@
         <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
@@ -3124,49 +3142,40 @@
       <c r="F6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="M6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="M7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="M8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
@@ -3181,52 +3190,46 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3234,9 +3237,9 @@
       <c r="E12" s="2"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -3244,12 +3247,12 @@
       <c r="E14" s="16"/>
       <c r="F14" s="17"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -3264,12 +3267,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
@@ -3281,106 +3284,76 @@
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
-      <c r="M18" t="s">
-        <v>203</v>
-      </c>
-      <c r="N18" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M19" t="s">
-        <v>189</v>
-      </c>
-      <c r="N19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="M20">
-        <v>230</v>
-      </c>
-      <c r="N20">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="3" t="s">
         <v>84</v>
@@ -3393,75 +3366,66 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M21">
-        <v>18</v>
-      </c>
-      <c r="N21">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="M23" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -3469,7 +3433,7 @@
       <c r="E26" s="16"/>
       <c r="F26" s="17"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -3489,12 +3453,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
@@ -3506,62 +3470,44 @@
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
-      <c r="M30" t="s">
-        <v>186</v>
-      </c>
-      <c r="N30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -3594,7 +3540,7 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -3604,22 +3550,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3627,70 +3573,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" t="s">
         <v>136</v>
-      </c>
-      <c r="H7" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -3701,7 +3647,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="3"/>
       <c r="H8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -3734,7 +3680,7 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -3767,7 +3713,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -3779,13 +3725,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
@@ -3795,48 +3741,48 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -3846,55 +3792,55 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -3907,7 +3853,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -3940,7 +3886,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
@@ -3952,13 +3898,13 @@
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>15</v>
@@ -3968,13 +3914,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
@@ -3984,39 +3930,39 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="4" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="303">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1051,10 +1051,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>orderState資料表(t_orderState)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>f_updateTime</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1169,32 +1165,81 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>創建時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(備註)更新時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingMethod</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前提供 1便利商店; 2:宅配</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_state</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示修改備註的時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_createTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>王六仔</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(326)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人電話號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>char(18)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期時間 (YYMMDD) + 時分秒轉成秒(00000~86399) + 會員碼最末7位(EX:0000001)  UNIQUE有唯一性
+  (Ex:250106000010000001 、 250107863990000002)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>orderProductStyle資料表(t_orderProductStyle)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>char(15)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>創建時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>(備註)更新時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippingMethod</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前提供 1便利商店; 2:宅配</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>orderState資料表(t_orderState)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>訂單更新就會生成對應state, ( 1:待確認, 
@@ -1203,60 +1248,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_state</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>表示修改備註的時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_createTime</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不管配送方式, 地址都須手動填寫</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>王六仔</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(326)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期時間 (YYMMDD) + 時分秒轉成秒(00000~86399) + 分類(2碼)+ 會員碼最末7位(EX:0000001)  UNIQUE有唯一性
-  (Ex:202501060300001 、 202501070500002)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人電話號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>電話號碼 (國內)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1465,6 +1461,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1473,15 +1478,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1807,14 +1803,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1967,14 +1963,14 @@
       <c r="F11" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2029,7 +2025,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2045,7 +2041,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2062,7 +2058,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2103,14 +2099,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2211,14 +2207,14 @@
         <v>156</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>301</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" t="s">
@@ -2293,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
@@ -2311,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -2323,14 +2319,14 @@
       <c r="F14" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2498,14 +2494,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="20"/>
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -2533,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>88</v>
@@ -2545,7 +2541,7 @@
         <v>47</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G3" s="13"/>
     </row>
@@ -2562,26 +2558,26 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2590,21 +2586,21 @@
         <v>96</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2612,9 +2608,11 @@
       <c r="D7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
       <c r="F7" s="14" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="G7">
         <v>0.1</v>
@@ -2636,7 +2634,7 @@
         <v>102</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2645,14 +2643,14 @@
         <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="G9" s="8"/>
     </row>
@@ -2662,7 +2660,7 @@
         <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>101</v>
@@ -2671,24 +2669,22 @@
       <c r="F10" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>297</v>
-      </c>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
@@ -2697,7 +2693,7 @@
     <row r="12" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>198</v>
@@ -2707,7 +2703,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2725,13 +2721,13 @@
         <v>185</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>184</v>
@@ -2743,10 +2739,10 @@
         <v>185</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2758,22 +2754,22 @@
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="20"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="17"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
+      <c r="A17" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2800,7 +2796,7 @@
         <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>88</v>
@@ -2828,7 +2824,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2844,7 +2840,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2872,14 +2868,14 @@
         <v>207</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2891,14 +2887,14 @@
       <c r="F24" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="17"/>
+      <c r="A26" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -2928,7 +2924,7 @@
         <v>249</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
@@ -2953,7 +2949,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
@@ -2967,9 +2963,11 @@
       <c r="D30" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
       <c r="F30" s="14" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2978,7 +2976,7 @@
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>198</v>
@@ -2988,16 +2986,16 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="4" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>215</v>
@@ -3006,16 +3004,16 @@
         <v>185</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>215</v>
@@ -3024,10 +3022,10 @@
         <v>185</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -3062,14 +3060,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3238,14 +3236,14 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -3343,14 +3341,14 @@
         <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3424,14 +3422,14 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="17"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -3539,14 +3537,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3679,14 +3677,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3760,7 +3758,7 @@
         <v>211</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3852,14 +3850,14 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
+      <c r="A14" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="322">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1214,18 +1214,6 @@
   </si>
   <si>
     <t>nvarchar(326)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人電話號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>電話號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>char(18)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1254,6 +1242,89 @@
   <si>
     <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨)</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>bigint</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人手機號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>freight資料表(t_freight)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_freightId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 1:便利商店; 2:宅配</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>運費金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_tagId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag資料表(t_tag)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(5)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_tagName</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>標籤名字</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_freeShipping</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>免運金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>標籤外鍵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingFee</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OriginalAmount DECIMAL(10, 2)</t>
+  </si>
+  <si>
+    <t>DiscountAmount DECIMAL(10, 2),</t>
+  </si>
+  <si>
+    <t>DiscountedAmount DECIMAL(10, 2),</t>
+  </si>
+  <si>
+    <t>ShippingFee DECIMAL(10, 2),</t>
+  </si>
+  <si>
+    <t>TotalAmount DECIMAL(10, 2)</t>
   </si>
 </sst>
 </file>
@@ -2214,7 +2285,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" t="s">
@@ -2482,7 +2553,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -2493,7 +2564,7 @@
     <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>231</v>
       </c>
@@ -2504,7 +2575,7 @@
       <c r="F1" s="20"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2524,7 +2595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2545,7 +2616,7 @@
       </c>
       <c r="G3" s="13"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
         <v>232</v>
@@ -2561,26 +2632,26 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
         <v>279</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G5" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
         <v>96</v>
@@ -2596,8 +2667,11 @@
         <v>274</v>
       </c>
       <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
         <v>286</v>
@@ -2612,13 +2686,16 @@
         <v>1</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G7">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
         <v>100</v>
@@ -2636,25 +2713,31 @@
       <c r="G8" s="8" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
         <v>104</v>
@@ -2670,8 +2753,11 @@
         <v>105</v>
       </c>
       <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
         <v>283</v>
@@ -2690,7 +2776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
         <v>255</v>
@@ -2706,7 +2792,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
         <v>221</v>
@@ -2724,7 +2810,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
         <v>253</v>
@@ -2745,7 +2831,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -2753,7 +2839,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
@@ -2763,7 +2849,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -2888,7 +2974,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -2967,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3668,7 +3754,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G21"/>
+  <dimension ref="A2:G36"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -3971,10 +4057,208 @@
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
     </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+      <c r="B27" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="20"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使用者表" sheetId="8" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="商品表" sheetId="5" r:id="rId4"/>
     <sheet name="交易紀錄表" sheetId="10" r:id="rId5"/>
     <sheet name="備用(淘汰的表)" sheetId="12" r:id="rId6"/>
+    <sheet name="待確認" sheetId="13" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="330">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -423,10 +424,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>f_totalPrice</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>f_orderId</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -555,31 +552,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>f_amount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>金額</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">f_transactionType </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>N</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex : 付款, 退款</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -763,10 +740,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>細項分類</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>圖片路徑</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -919,38 +892,34 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>f_createTime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>退貨單狀態 (已確認/取消</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>productImage資料表(t_productImage)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productImageId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據行名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>f_productStyleId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_createTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>decimal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>退貨單狀態 (已確認/取消</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>productImage資料表(t_productImage)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productImageId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據行名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productStyleId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>productStyle資料表(t_productStyle)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1083,19 +1052,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>f_orderProductStyleId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>會員表外鍵</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>訂單表外鍵</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>商品子項目 (細項) 表外鍵</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1177,14 +1138,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前提供 1便利商店; 2:宅配</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>f_state</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1194,22 +1147,6 @@
   </si>
   <si>
     <t>f_createTime</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>王六仔</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1220,10 +1157,6 @@
     <t>日期時間 (YYMMDD) + 時分秒轉成秒(00000~86399) + 會員碼最末7位(EX:0000001)  UNIQUE有唯一性
   (Ex:250106000010000001 、 250107863990000002)</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderProductStyle資料表(t_orderProductStyle)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>orderState資料表(t_orderState)</t>
@@ -1236,95 +1169,200 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>bigint</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人手機號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>freight資料表(t_freight)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_freightId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 1:便利商店; 2:宅配</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>運費金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_freeShipping</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>免運金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingFee</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>細項名稱</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品外鍵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_originalAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>原價</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_discountAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_discountedAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣的金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣後的金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippintFee</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>運費</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_totalAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>總金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderItem資料表(t_orderItem)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_originalAmount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>原始金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣後金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>bigint</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人手機號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>手機號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>freight資料表(t_freight)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_freightId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>運輸方式 1:便利商店; 2:宅配</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>運費金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_tagId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>tag資料表(t_tag)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(5)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_tagName</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>標籤名字</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_freeShipping</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>免運金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>標籤外鍵</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_totalAmount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(30)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_discountAmount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_option</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingOption</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 :便利商店; 宅配</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式:便利商店; 宅配</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改運費時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GETDATE()</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_updateTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>shippingOption資料表(t_shippingOption)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingOptionId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>f_shippingFee</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OriginalAmount DECIMAL(10, 2)</t>
-  </si>
-  <si>
-    <t>DiscountAmount DECIMAL(10, 2),</t>
-  </si>
-  <si>
-    <t>DiscountedAmount DECIMAL(10, 2),</t>
-  </si>
-  <si>
-    <t>ShippingFee DECIMAL(10, 2),</t>
-  </si>
-  <si>
-    <t>TotalAmount DECIMAL(10, 2)</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1524,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1526,20 +1564,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1874,14 +1900,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1908,7 +1934,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -2034,14 +2060,14 @@
       <c r="F11" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
+      <c r="A13" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2068,7 +2094,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>55</v>
@@ -2096,7 +2122,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2112,7 +2138,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2128,8 +2154,8 @@
         <v>35</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="14" t="s">
-        <v>269</v>
+      <c r="F18" s="13" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2170,14 +2196,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2204,7 +2230,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -2238,7 +2264,7 @@
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
@@ -2255,17 +2281,17 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7">
@@ -2275,46 +2301,46 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>33</v>
@@ -2324,13 +2350,13 @@
         <v>34</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>26</v>
@@ -2348,10 +2374,10 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
@@ -2360,16 +2386,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>9</v>
@@ -2377,8 +2403,8 @@
       <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>267</v>
+      <c r="F13" s="13" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -2390,14 +2416,14 @@
       <c r="F14" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20"/>
+      <c r="A17" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2424,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>7</v>
@@ -2461,7 +2487,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
@@ -2471,16 +2497,16 @@
         <v>28</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>21</v>
@@ -2490,35 +2516,35 @@
         <v>29</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>9</v>
@@ -2553,7 +2579,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -2564,18 +2590,17 @@
     <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2595,12 +2620,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>88</v>
@@ -2612,14 +2637,13 @@
         <v>47</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="13"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>88</v>
@@ -2629,504 +2653,653 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="64.8" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="G5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3" t="s">
-        <v>96</v>
+      <c r="F5" s="13" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="4" t="s">
+        <v>274</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="I6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="G7">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="I8" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="I9" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="4" t="s">
         <v>104</v>
       </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="C10" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>101</v>
+        <v>263</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="I10" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="4" t="s">
-        <v>283</v>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>284</v>
+        <v>263</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>198</v>
+        <v>316</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="14" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F12" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>184</v>
+        <v>263</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="17"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="E16" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="F22" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="B24" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="4" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="C36" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="6"/>
+      <c r="B37" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="6"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B42" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E30" s="2">
-        <v>1</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="4" t="s">
+      <c r="F42" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="6"/>
+      <c r="B45" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="6"/>
+      <c r="B46" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="6"/>
+      <c r="B47" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>324</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A26:F26"/>
+  <mergeCells count="4">
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3146,14 +3319,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3180,17 +3353,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -3202,13 +3375,13 @@
         <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -3217,7 +3390,7 @@
         <v>77</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
@@ -3233,30 +3406,30 @@
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3274,43 +3447,43 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3322,21 +3495,21 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+      <c r="A14" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
@@ -3356,7 +3529,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
@@ -3368,7 +3541,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -3377,30 +3550,30 @@
         <v>83</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
@@ -3408,17 +3581,17 @@
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>181</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -3427,14 +3600,14 @@
         <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3450,7 +3623,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -3459,63 +3632,63 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
+      <c r="A26" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -3542,7 +3715,7 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
@@ -3554,39 +3727,39 @@
         <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
@@ -3614,7 +3787,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表6"/>
-  <dimension ref="A2:H9"/>
+  <dimension ref="A2:H11"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -3623,33 +3796,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3657,90 +3830,130 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="3" t="s">
-        <v>129</v>
+      <c r="B6" t="s">
+        <v>296</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>130</v>
+        <v>263</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>131</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>132</v>
+        <v>300</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>135</v>
+        <v>301</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>304</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3754,7 +3967,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G36"/>
+  <dimension ref="A2:G30"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -3763,14 +3976,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3797,7 +4010,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -3809,13 +4022,13 @@
         <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
@@ -3825,48 +4038,48 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -3876,55 +4089,55 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -3936,14 +4149,14 @@
       <c r="F12" s="3"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+      <c r="A14" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -3970,7 +4183,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>7</v>
@@ -3982,13 +4195,13 @@
         <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>15</v>
@@ -3998,13 +4211,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>15</v>
@@ -4014,39 +4227,39 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -4058,14 +4271,14 @@
       <c r="F21" s="3"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
+      <c r="A23" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -4092,7 +4305,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
@@ -4104,13 +4317,13 @@
         <v>8</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>15</v>
@@ -4120,13 +4333,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -4136,39 +4349,39 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -4179,89 +4392,42 @@
       <c r="E30" s="2"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="20"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A6:B35"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="47.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="331">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1163,205 +1163,209 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>bigint</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人手機號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機號碼 (國內)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>freight資料表(t_freight)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_freightId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 1:便利商店; 2:宅配</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>運費金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_freeShipping</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>免運金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingFee</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>細項名稱</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品外鍵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_originalAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>原價</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_discountAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_discountedAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣的金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣後的金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippintFee</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>運費</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_totalAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>總金額</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_productName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_orderItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orderItem資料表(t_orderItem)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_originalAmount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>原始金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>折扣後金額  (小數點前8位 小數點後2位)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_totalAmount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>nvarchar(30)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_discountAmount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_option</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingOption</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 :便利商店; 宅配</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式:便利商店; 宅配</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改運費時間</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GETDATE()</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_updateTime</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>shippingOption資料表(t_shippingOption)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingOptionId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingFee</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>訂單更新就會生成對應state, ( 1:待確認, 
 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 
-6:重新寄回, 7:取消, 8:退貨)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>bigint</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人手機號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>手機號碼 (國內)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>freight資料表(t_freight)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_freightId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>運輸方式 1:便利商店; 2:宅配</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>運費金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_freeShipping</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>免運金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippingFee</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>細項名稱</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>商品外鍵</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_originalAmount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>原價</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_discountAmount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_discountedAmount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>折扣的金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>折扣後的金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippintFee</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>運費</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_totalAmount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>總金額</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_productName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_orderItemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>orderItem資料表(t_orderItem)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_originalAmount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>原始金額  (小數點前8位 小數點後2位)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>折扣後金額  (小數點前8位 小數點後2位)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_totalAmount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(10)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>nvarchar(30)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_discountAmount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_option</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippingOption</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>運輸方式 :便利商店; 宅配</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>運輸方式:便利商店; 宅配</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>生成時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改運費時間</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>GETDATE()</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+6:重新寄回, 7:取消, 8:退貨, 9:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨, 9:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>f_updateTime</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>shippingOption資料表(t_shippingOption)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippingOptionId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippingFee</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" t="s">
@@ -2662,7 +2666,7 @@
         <v>269</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
@@ -2672,7 +2676,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="4" t="s">
         <v>274</v>
@@ -2687,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>281</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2741,7 +2745,7 @@
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>263</v>
@@ -2751,13 +2755,13 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>263</v>
@@ -2767,29 +2771,29 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>263</v>
@@ -2799,13 +2803,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>263</v>
@@ -2855,7 +2859,7 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="4" t="s">
-        <v>245</v>
+        <v>330</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>177</v>
@@ -2880,7 +2884,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -2913,7 +2917,7 @@
         <v>93</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>88</v>
@@ -2947,10 +2951,10 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>9</v>
@@ -2973,7 +2977,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -3097,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -3162,7 +3166,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -3195,10 +3199,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>9</v>
@@ -3213,7 +3217,7 @@
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>112</v>
@@ -3223,13 +3227,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>263</v>
@@ -3239,13 +3243,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>263</v>
@@ -3255,7 +3259,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3270,16 +3274,16 @@
         <v>100</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>246</v>
@@ -3291,7 +3295,7 @@
         <v>178</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -3864,7 +3868,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>263</v>
@@ -3874,13 +3878,13 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>263</v>
@@ -3890,7 +3894,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H7" t="s">
         <v>130</v>
@@ -3899,17 +3903,17 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H8" t="s">
         <v>131</v>
@@ -3918,33 +3922,33 @@
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4272,7 +4276,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -4305,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
@@ -4323,7 +4327,7 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>15</v>
@@ -4333,7 +4337,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -4349,13 +4353,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>214</v>
@@ -4365,23 +4369,23 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="338">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1138,10 +1138,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>f_state</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>表示修改備註的時間</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1311,22 +1307,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>f_option</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>f_shippingOption</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>運輸方式 :便利商店; 宅配</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>運輸方式:便利商店; 宅配</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>生成時間</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1355,18 +1335,64 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>訂單更新就會生成對應state, ( 1:待確認, 
-2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 
-6:重新寄回, 7:取消, 8:退貨, 9:退款)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:完成, 5:買家未取商品, 6:重新寄回, 7:取消, 8:退貨, 9:退款)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>f_updateTime</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_optionName</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_currentState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_previousState</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>上個訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:包裹已抵達, 5:完成, 6:買家未取商品, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前訂單狀態  ( 1:待確認, 2:待出貨, 3:已出貨, 4:包裹已抵達, 5:完成, 6:買家未取商品, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單更新就會生成對應state, ( 1:待確認, 2:待出貨, 3:已出貨, 4:包裹已抵達, 5:完成, 6:買家未取商品, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_shippingOptionName</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>物流對應的編號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 :7-ELEVEN; 全家; 黑貓宅急便</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>'</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>f_logisticsNumber</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>運輸方式 :7-ELEVEN; 全家; 黑貓宅急便</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2315,7 +2341,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" t="s">
@@ -2583,7 +2609,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表5"/>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.21875" customWidth="1"/>
@@ -2666,20 +2692,20 @@
         <v>269</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
-        <v>274</v>
+      <c r="A6" s="7"/>
+      <c r="B6" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -2688,80 +2714,82 @@
         <v>89</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>325</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>281</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>277</v>
+        <v>110</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="3" t="s">
-        <v>309</v>
+      <c r="A10" s="6"/>
+      <c r="B10" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>89</v>
+        <v>276</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>310</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>263</v>
@@ -2771,539 +2799,581 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="4" t="s">
-        <v>318</v>
+      <c r="A12" s="5"/>
+      <c r="B12" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>100</v>
+        <v>263</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>263</v>
+        <v>313</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
-        <v>286</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="3" t="s">
-        <v>313</v>
+      <c r="A14" s="6"/>
+      <c r="B14" s="4" t="s">
+        <v>289</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>89</v>
+      <c r="D14" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="13" t="s">
-        <v>256</v>
-      </c>
-    </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="4" t="s">
-        <v>213</v>
+      <c r="A16" s="7"/>
+      <c r="B16" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>178</v>
+        <v>331</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="4" t="s">
-        <v>330</v>
+        <v>247</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-    </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A20" s="5"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
       <c r="B24" s="3" t="s">
         <v>306</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>315</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3" t="s">
-        <v>78</v>
+        <v>35</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>291</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="4" t="s">
-        <v>237</v>
+      <c r="A26" s="5"/>
+      <c r="B26" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>110</v>
+        <v>314</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>238</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="4" t="s">
-        <v>200</v>
+      <c r="A27" s="5"/>
+      <c r="B27" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>265</v>
+        <v>170</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A30" s="6"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="3" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="4" t="s">
-        <v>276</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+      <c r="B36" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>270</v>
+        <v>243</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>178</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" s="3" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
+      <c r="B38" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="6"/>
+      <c r="B39" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A40" s="6"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="B44" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C43" s="3" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+      <c r="B45" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="4" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>323</v>
-      </c>
+      <c r="E46" s="2"/>
       <c r="F46" s="3" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="4" t="s">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="2"/>
+      <c r="F47" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="6"/>
+      <c r="B48" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="6"/>
+      <c r="B49" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>322</v>
-      </c>
+      <c r="F49" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="6"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3595,7 +3665,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -3868,7 +3938,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>263</v>
@@ -3878,13 +3948,13 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>263</v>
@@ -3894,7 +3964,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H7" t="s">
         <v>130</v>
@@ -3903,17 +3973,17 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H8" t="s">
         <v>131</v>
@@ -3922,33 +3992,33 @@
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4276,7 +4346,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -4309,7 +4379,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
@@ -4327,7 +4397,7 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>15</v>
@@ -4337,7 +4407,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -4353,13 +4423,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>214</v>
@@ -4369,23 +4439,23 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">

--- a/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
+++ b/document/ProjectUsing/SqlDataTableNotes/資料表設計.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="337">
   <si>
     <t>KEY</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1060,10 +1060,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>訂單表外鍵</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>備註 (舉例:幾點要出貨, 或者說是取消訂單的原因...等等)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1351,18 +1347,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>上個訂單狀態 ( 1:待確認, 2:待出貨, 3:已出貨, 4:包裹已抵達, 5:完成, 6:買家未取商品, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前訂單狀態  ( 1:待確認, 2:待出貨, 3:已出貨, 4:包裹已抵達, 5:完成, 6:買家未取商品, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>訂單更新就會生成對應state, ( 1:待確認, 2:待出貨, 3:已出貨, 4:包裹已抵達, 5:完成, 6:買家未取商品, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>f_shippingOptionName</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1393,6 +1377,18 @@
   <si>
     <t>運輸方式 :7-ELEVEN; 全家; 黑貓宅急便</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前訂單狀態  ( 1:待確認, 2:申請取消, 3:待出貨, 4:已出貨, 5:已到貨, 6:完成, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>上個訂單狀態 ( 1:待確認, 2:申請取消, 3:待出貨, 4:已出貨, 5:已到貨, 6:完成, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂單更新就會生成對應state, ( 1:待確認, 2:申請取消, 3:待出貨, 4:已出貨, 5:已到貨, 6:完成, 7:取消, 8:申請退貨, 9:退貨, 10:退款)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2152,7 +2148,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2168,7 +2164,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G17" s="9"/>
     </row>
@@ -2185,7 +2181,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2341,7 +2337,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" t="s">
@@ -2416,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="32.4" x14ac:dyDescent="0.3">
@@ -2434,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -2689,23 +2685,23 @@
     <row r="5" spans="1:6" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -2717,13 +2713,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -2735,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2767,7 +2763,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2776,7 +2772,7 @@
         <v>103</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>100</v>
@@ -2789,99 +2785,99 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>335</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2897,7 +2893,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2915,13 +2911,13 @@
         <v>178</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>177</v>
@@ -2933,7 +2929,7 @@
         <v>178</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2946,7 +2942,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -2979,7 +2975,7 @@
         <v>93</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>88</v>
@@ -3013,10 +3009,10 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
@@ -3039,7 +3035,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -3064,14 +3060,14 @@
         <v>200</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3084,7 +3080,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -3145,7 +3141,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -3163,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -3179,13 +3175,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>246</v>
@@ -3197,7 +3193,7 @@
         <v>178</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3215,7 +3211,7 @@
         <v>178</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -3228,7 +3224,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -3261,10 +3257,10 @@
         <v>6</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>9</v>
@@ -3279,7 +3275,7 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>112</v>
@@ -3289,45 +3285,45 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>246</v>
@@ -3336,16 +3332,16 @@
         <v>100</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>246</v>
@@ -3357,7 +3353,7 @@
         <v>178</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3665,7 +3661,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -3674,14 +3670,14 @@
         <v>79</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3938,33 +3934,33 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>129</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H7" t="s">
         <v>130</v>
@@ -3973,17 +3969,17 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H8" t="s">
         <v>131</v>
@@ -3992,33 +3988,33 @@
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4346,7 +4342,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -4379,7 +4375,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
@@ -4397,7 +4393,7 @@
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>15</v>
@@ -4407,13 +4403,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>25</v>
@@ -4423,13 +4419,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>214</v>
@@ -4439,23 +4435,23 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
